--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486402_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486402_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.684799999999999</v>
+        <v>8.710599999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8035</v>
+        <v>4.6616</v>
       </c>
       <c r="F2" t="n">
-        <v>4.8813</v>
+        <v>4.049</v>
       </c>
       <c r="G2" t="n">
         <v>2.6311</v>
@@ -610,13 +610,13 @@
         <v>4.1326</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0086</v>
+        <v>1.0344</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3953</v>
+        <v>0.4627</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4039</v>
+        <v>0.5717</v>
       </c>
       <c r="V2" t="n">
         <v>1.13</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.0037</v>
+        <v>6.4761</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9747</v>
+        <v>4.3547</v>
       </c>
       <c r="F3" t="n">
-        <v>2.029</v>
+        <v>2.1215</v>
       </c>
       <c r="G3" t="n">
         <v>2.6733</v>
@@ -688,13 +688,13 @@
         <v>2.3926</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4833</v>
+        <v>0.9556</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5622</v>
+        <v>0.9421</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.079</v>
+        <v>0.0135</v>
       </c>
       <c r="V3" t="n">
         <v>2.6297</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4425</v>
+        <v>2.8454</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2372</v>
+        <v>1.4859</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2054</v>
+        <v>1.3595</v>
       </c>
       <c r="G4" t="n">
         <v>1.9151</v>
@@ -766,13 +766,13 @@
         <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5377999999999999</v>
+        <v>-0.1349</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.411</v>
+        <v>-0.1622</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1268</v>
+        <v>0.0273</v>
       </c>
       <c r="V4" t="n">
         <v>0.1952</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8845</v>
+        <v>2.1015</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1776</v>
+        <v>0.2713</v>
       </c>
       <c r="F5" t="n">
-        <v>1.707</v>
+        <v>1.8302</v>
       </c>
       <c r="G5" t="n">
         <v>1.1887</v>
@@ -844,13 +844,13 @@
         <v>3.0451</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3047</v>
+        <v>-0.0877</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1334</v>
+        <v>-0.0396</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1714</v>
+        <v>-0.0481</v>
       </c>
       <c r="V5" t="n">
         <v>-0.7395</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6389</v>
+        <v>0.9523</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.6328</v>
+        <v>-0.9802999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2717</v>
+        <v>1.9326</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4606</v>
@@ -922,13 +922,13 @@
         <v>2.3926</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2056</v>
+        <v>0.1078</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.0204</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4673</v>
+        <v>0.1283</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4987</v>
+        <v>0.467</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3679</v>
+        <v>0.2129</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1308</v>
+        <v>0.2541</v>
       </c>
       <c r="G7" t="n">
         <v>0.896</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6903</v>
+        <v>0.6585</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7571</v>
+        <v>0.6021</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0668</v>
+        <v>0.0565</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0493</v>
+        <v>0.28</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4789</v>
+        <v>-0.2482</v>
       </c>
       <c r="F8" t="n">
         <v>0.5283</v>
@@ -1078,10 +1078,10 @@
         <v>1.7401</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3785</v>
+        <v>0.6093</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2211</v>
+        <v>0.4518</v>
       </c>
       <c r="U8" t="n">
         <v>0.1574</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7465</v>
+        <v>-1.4563</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.4548</v>
+        <v>-4.4728</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7083</v>
+        <v>3.0166</v>
       </c>
       <c r="G9" t="n">
         <v>-1.837</v>
@@ -1156,13 +1156,13 @@
         <v>3.2626</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0481</v>
+        <v>0.3383</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3942</v>
+        <v>0.3761</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3461</v>
+        <v>-0.0379</v>
       </c>
       <c r="V9" t="n">
         <v>1.13</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. VICEDO AYALA</t>
+          <t>E. WEMBI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.932</v>
+        <v>-1.5332</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4158</v>
+        <v>-1.7134</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5161</v>
+        <v>0.1803</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9883</v>
+        <v>-0.391</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2615</v>
+        <v>0.1947</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7267</v>
+        <v>-0.5857</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1228</v>
+        <v>0.3948</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1611</v>
+        <v>0.2801</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0382</v>
+        <v>0.1147</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8653999999999999</v>
+        <v>-0.7858000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1004</v>
+        <v>-0.0854</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.765</v>
+        <v>-0.7004</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2175</v>
+        <v>1.9576</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0737</v>
+        <v>-0.0997</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2055</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1318</v>
+        <v>-0.0361</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>E. WEMBI</t>
+          <t>E. VICEDO AYALA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3205</v>
+        <v>-1.9559</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2542</v>
+        <v>-1.3474</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0663</v>
+        <v>-0.6086</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.391</v>
+        <v>-0.9883</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1947</v>
+        <v>-0.2615</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5857</v>
+        <v>-0.7267</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3948</v>
+        <v>-0.1228</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2801</v>
+        <v>-0.1611</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1147</v>
+        <v>0.0382</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7858000000000001</v>
+        <v>-0.8653999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0854</v>
+        <v>-0.1004</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7004</v>
+        <v>-0.765</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6525</v>
+        <v>-0.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.305</v>
+        <v>-1.0875</v>
       </c>
       <c r="R11" t="n">
-        <v>1.9576</v>
+        <v>0.2175</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8871</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6044</v>
+        <v>-0.137</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2826</v>
+        <v>0.0394</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.9554</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.3973</v>
+        <v>-4.6841</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.6744</v>
+        <v>-5.1769</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2771</v>
+        <v>0.4929</v>
       </c>
       <c r="G12" t="n">
         <v>-4.1782</v>
@@ -1390,13 +1390,13 @@
         <v>1.7401</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3921</v>
+        <v>0.3212</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1334</v>
+        <v>0.3641</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2587</v>
+        <v>-0.043</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1745</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.806100000000001</v>
+        <v>12.20339999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.350000000000001</v>
+        <v>-2.952599999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>15.1565</v>
+        <v>15.1564</v>
       </c>
       <c r="G13" t="n">
         <v>-0.4027000000000003</v>
@@ -1459,7 +1459,7 @@
         <v>-1.789</v>
       </c>
       <c r="P13" t="n">
-        <v>6.5252</v>
+        <v>6.525200000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-15.2253</v>
@@ -1468,13 +1468,13 @@
         <v>21.7508</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2078</v>
+        <v>3.6052</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3787</v>
+        <v>2.776</v>
       </c>
       <c r="U13" t="n">
-        <v>0.829</v>
+        <v>0.8289999999999998</v>
       </c>
       <c r="V13" t="n">
         <v>2.475899999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.077</v>
+        <v>3.0687</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8064</v>
+        <v>1.2534</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2707</v>
+        <v>1.8153</v>
       </c>
       <c r="G14" t="n">
         <v>3.5707</v>
@@ -1546,13 +1546,13 @@
         <v>1.9576</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2332</v>
+        <v>-0.2415</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4795</v>
+        <v>-0.0324</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7537</v>
+        <v>-0.2091</v>
       </c>
       <c r="V14" t="n">
         <v>0.1745</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. NGOM</t>
+          <t>A. ZUBIZARRETA ARANBARRI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6888</v>
+        <v>0.443</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9861</v>
+        <v>-0.2541</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7027</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>5.7984</v>
+        <v>-0.7436</v>
       </c>
       <c r="H15" t="n">
-        <v>6.2287</v>
+        <v>1.0645</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4303</v>
+        <v>-1.8081</v>
       </c>
       <c r="J15" t="n">
-        <v>5.4965</v>
+        <v>-0.3587</v>
       </c>
       <c r="K15" t="n">
-        <v>5.42</v>
+        <v>1.1315</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0765</v>
+        <v>-1.4901</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3019</v>
+        <v>-0.3849</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8087</v>
+        <v>-0.067</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5068</v>
+        <v>-0.318</v>
       </c>
       <c r="P15" t="n">
-        <v>-5.2202</v>
+        <v>0.2175</v>
       </c>
       <c r="Q15" t="n">
-        <v>-6.7427</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5225</v>
+        <v>0.2175</v>
       </c>
       <c r="S15" t="n">
-        <v>2.9801</v>
+        <v>0.2295</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9718</v>
+        <v>0.1046</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0083</v>
+        <v>0.125</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.8695</v>
+        <v>0.7395</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.7395</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.13</v>
+        <v>0.7395</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. ZUBIZARRETA ARANBARRI</t>
+          <t>O. HANZLIK</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7667</v>
+        <v>0.1164</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1929</v>
+        <v>-1.1726</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5738</v>
+        <v>1.289</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7436</v>
+        <v>-0.7617</v>
       </c>
       <c r="H16" t="n">
-        <v>1.0645</v>
+        <v>0.0941</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.8081</v>
+        <v>-0.8558</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3587</v>
+        <v>-0.9034</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1315</v>
+        <v>0.146</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.4901</v>
+        <v>-1.0494</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3849</v>
+        <v>0.1417</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.067</v>
+        <v>-0.0519</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.318</v>
+        <v>0.1936</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5533</v>
+        <v>-0.2094</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5516</v>
+        <v>-0.2692</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0017</v>
+        <v>0.0598</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.7395</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. HANZLIK</t>
+          <t>A. NGOM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2754</v>
+        <v>-0.3164</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.5079</v>
+        <v>-1.1373</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2325</v>
+        <v>0.8209</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7617</v>
+        <v>5.7984</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0941</v>
+        <v>6.2287</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8558</v>
+        <v>-0.4303</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9034</v>
+        <v>5.4965</v>
       </c>
       <c r="K17" t="n">
-        <v>0.146</v>
+        <v>5.42</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.0494</v>
+        <v>0.0765</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1417</v>
+        <v>0.3019</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0519</v>
+        <v>0.8087</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1936</v>
+        <v>-0.5068</v>
       </c>
       <c r="P17" t="n">
-        <v>1.0875</v>
+        <v>-5.2202</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-6.7427</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0875</v>
+        <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6012</v>
+        <v>0.9749</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6044</v>
+        <v>0.8484</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0032</v>
+        <v>0.1265</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.8695</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.7395</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0801</v>
+        <v>-0.6459</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3068</v>
+        <v>-1.0833</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2267</v>
+        <v>0.4373</v>
       </c>
       <c r="G18" t="n">
         <v>0.5503</v>
@@ -1858,13 +1858,13 @@
         <v>0.2175</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7604</v>
+        <v>-0.3263</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.274</v>
+        <v>-0.0505</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4864</v>
+        <v>-0.2758</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. NICOLAU ALEDON</t>
+          <t>M. ANSORREGUI DEBA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4398</v>
+        <v>-0.6985</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2479</v>
+        <v>-2.0703</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1918</v>
+        <v>1.3718</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.5888</v>
+        <v>-0.9785</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.4238</v>
+        <v>-1.5387</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.165</v>
+        <v>0.5602</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4069</v>
+        <v>-0.4325</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.5599</v>
+        <v>-1.7329</v>
       </c>
       <c r="L19" t="n">
-        <v>0.153</v>
+        <v>1.3005</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1819</v>
+        <v>-0.5461</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8639</v>
+        <v>0.1943</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.318</v>
+        <v>-0.7403</v>
       </c>
       <c r="P19" t="n">
-        <v>1.0875</v>
+        <v>0.6525</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R19" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0822</v>
+        <v>-0.3725</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3184</v>
+        <v>-0.3329</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4006</v>
+        <v>-0.0397</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0207</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.695</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. ANSORREGUI DEBA</t>
+          <t>J. NICOLAU ALEDON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7904</v>
+        <v>-1.3639</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.7409</v>
+        <v>-0.1362</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9505</v>
+        <v>-1.2278</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9785</v>
+        <v>-2.5888</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5387</v>
+        <v>-2.4238</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5602</v>
+        <v>-0.165</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4325</v>
+        <v>-1.4069</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.7329</v>
+        <v>-1.5599</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3005</v>
+        <v>0.153</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5461</v>
+        <v>-1.1819</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1943</v>
+        <v>-0.8639</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7403</v>
+        <v>-0.318</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4644</v>
+        <v>0.158</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0034</v>
+        <v>-0.2067</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.461</v>
+        <v>0.3647</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.0207</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.695</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.7156</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4539</v>
+        <v>-1.9195</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6131</v>
+        <v>-1.1661</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8408</v>
+        <v>-0.7534</v>
       </c>
       <c r="G21" t="n">
         <v>-2.7368</v>
@@ -2092,13 +2092,13 @@
         <v>2.1751</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7177</v>
+        <v>-0.1833</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9349</v>
+        <v>-0.4879</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2173</v>
+        <v>0.3046</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7395</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.645</v>
+        <v>-2.9873</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3137</v>
+        <v>-3.8666</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6687</v>
+        <v>0.8794</v>
       </c>
       <c r="G22" t="n">
         <v>0.0063</v>
@@ -2170,13 +2170,13 @@
         <v>2.6101</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.716</v>
+        <v>-0.0583</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.2944</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0255</v>
+        <v>0.2361</v>
       </c>
       <c r="V22" t="n">
         <v>-0.7602</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6543</v>
+        <v>-4.0126</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.4114</v>
+        <v>-5.5232</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7571</v>
+        <v>1.5105</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7138</v>
@@ -2248,13 +2248,13 @@
         <v>2.1751</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6696</v>
+        <v>0.3112</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0036</v>
+        <v>-0.1081</v>
       </c>
       <c r="U23" t="n">
-        <v>0.666</v>
+        <v>0.4194</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,25 +2281,25 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.8064</v>
+        <v>-8.315999999999999</v>
       </c>
       <c r="E24" t="n">
         <v>-15.1563</v>
       </c>
       <c r="F24" t="n">
-        <v>5.350099999999999</v>
+        <v>6.8401</v>
       </c>
       <c r="G24" t="n">
         <v>0.4024999999999994</v>
       </c>
       <c r="H24" t="n">
-        <v>1.9923</v>
+        <v>1.992300000000002</v>
       </c>
       <c r="I24" t="n">
         <v>-1.5898</v>
       </c>
       <c r="J24" t="n">
-        <v>5.882200000000001</v>
+        <v>5.8822</v>
       </c>
       <c r="K24" t="n">
         <v>4.093299999999997</v>
@@ -2308,7 +2308,7 @@
         <v>1.7892</v>
       </c>
       <c r="M24" t="n">
-        <v>-5.479799999999999</v>
+        <v>-5.4798</v>
       </c>
       <c r="N24" t="n">
         <v>-2.1009</v>
@@ -2317,7 +2317,7 @@
         <v>-3.379</v>
       </c>
       <c r="P24" t="n">
-        <v>-6.525300000000001</v>
+        <v>-6.5253</v>
       </c>
       <c r="Q24" t="n">
         <v>-21.7507</v>
@@ -2326,13 +2326,13 @@
         <v>15.2255</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.2077</v>
+        <v>0.2822999999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8289999999999996</v>
+        <v>-0.8290999999999997</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3784999999999999</v>
+        <v>1.1115</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4759</v>
